--- a/orbita-kit/source/План-график_этап1_ЯМГ-ИИМ.xlsx
+++ b/orbita-kit/source/План-график_этап1_ЯМГ-ИИМ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavel Klemmer\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A411D26F-27A3-4A31-BA46-F82DA7A437F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C35A9B1-2BA5-4F42-B6EE-364B753B8C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="План-график (На подписание)" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="465">
   <si>
     <t>План-график мероприятий по выполнению этапа ОКР</t>
   </si>
@@ -1082,18 +1082,6 @@
     <t>2.1.5.</t>
   </si>
   <si>
-    <t>Подготовка материалов</t>
-  </si>
-  <si>
-    <t>Решить проблему с размещением, ждем пакет документов на согласование</t>
-  </si>
-  <si>
-    <t>Идет процесс, срок 30.09.2026</t>
-  </si>
-  <si>
-    <t>Ждем, финальная проработка документов</t>
-  </si>
-  <si>
     <t>СРЕДНЕСРОЧНЫЕ РАБОТЫ — горизонт 1 месяц (01.10.2026 — 31.10.2026).</t>
   </si>
   <si>
@@ -1427,13 +1415,22 @@
     <t xml:space="preserve">ВСЕГО по статье «Сырье и материалы» </t>
   </si>
   <si>
-    <t xml:space="preserve">Документ не получили </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Подготовка материалов, ждем финальную версию </t>
-  </si>
-  <si>
-    <t>Согласовано</t>
+    <t>Принято, замечания отработаны</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Взяли в работу </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Запуск конкурса и информирвоание по результатам </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Процесс согласования документов </t>
+  </si>
+  <si>
+    <t>Срок прошел 30.09.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В работе </t>
   </si>
 </sst>
 </file>
@@ -1444,7 +1441,7 @@
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -1585,12 +1582,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1601,8 +1592,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1625,12 +1622,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1741,36 +1749,102 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1781,27 +1855,21 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1814,49 +1882,16 @@
     <xf numFmtId="44" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2888,67 +2923,67 @@
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:9" ht="166.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
       <c r="H3" s="13"/>
       <c r="I3" s="13"/>
     </row>
     <row r="4" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
     </row>
     <row r="7" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
     </row>
@@ -3229,16 +3264,16 @@
       <c r="A19" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="64"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="64"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="64"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
@@ -3268,13 +3303,13 @@
       <c r="D21" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E21" s="40" t="s">
+      <c r="E21" s="66" t="s">
         <v>68</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G21" s="42" t="s">
+      <c r="G21" s="68" t="s">
         <v>69</v>
       </c>
       <c r="H21" s="5" t="s">
@@ -3295,11 +3330,11 @@
       <c r="D22" s="31">
         <v>46269</v>
       </c>
-      <c r="E22" s="41"/>
+      <c r="E22" s="64"/>
       <c r="F22" s="31">
         <v>46269</v>
       </c>
-      <c r="G22" s="41"/>
+      <c r="G22" s="64"/>
       <c r="H22" s="5" t="s">
         <v>73</v>
       </c>
@@ -3318,11 +3353,11 @@
       <c r="D23" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="41"/>
+      <c r="E23" s="64"/>
       <c r="F23" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="41"/>
+      <c r="G23" s="64"/>
       <c r="H23" s="5" t="s">
         <v>78</v>
       </c>
@@ -3341,11 +3376,11 @@
       <c r="D24" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E24" s="41"/>
+      <c r="E24" s="64"/>
       <c r="F24" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G24" s="41"/>
+      <c r="G24" s="64"/>
       <c r="H24" s="5" t="s">
         <v>78</v>
       </c>
@@ -3364,11 +3399,11 @@
       <c r="D25" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="E25" s="41"/>
+      <c r="E25" s="64"/>
       <c r="F25" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G25" s="41"/>
+      <c r="G25" s="64"/>
       <c r="H25" s="5" t="s">
         <v>85</v>
       </c>
@@ -3389,11 +3424,11 @@
       <c r="D26" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E26" s="41"/>
+      <c r="E26" s="64"/>
       <c r="F26" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G26" s="41"/>
+      <c r="G26" s="64"/>
       <c r="H26" s="5" t="s">
         <v>89</v>
       </c>
@@ -3412,13 +3447,13 @@
       <c r="D27" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E27" s="40" t="s">
+      <c r="E27" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="F27" s="42" t="s">
+      <c r="F27" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="G27" s="42" t="s">
+      <c r="G27" s="68" t="s">
         <v>69</v>
       </c>
       <c r="H27" s="5" t="s">
@@ -3439,9 +3474,9 @@
       <c r="D28" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="64"/>
       <c r="H28" s="5" t="s">
         <v>97</v>
       </c>
@@ -3460,9 +3495,9 @@
       <c r="D29" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
+      <c r="E29" s="64"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
       <c r="H29" s="5" t="s">
         <v>100</v>
       </c>
@@ -3481,9 +3516,9 @@
       <c r="D30" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
+      <c r="E30" s="64"/>
+      <c r="F30" s="64"/>
+      <c r="G30" s="64"/>
       <c r="H30" s="5" t="s">
         <v>104</v>
       </c>
@@ -3502,9 +3537,9 @@
       <c r="D31" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
+      <c r="E31" s="64"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="64"/>
       <c r="H31" s="5" t="s">
         <v>107</v>
       </c>
@@ -3523,9 +3558,9 @@
       <c r="D32" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
+      <c r="E32" s="64"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="64"/>
       <c r="H32" s="5" t="s">
         <v>110</v>
       </c>
@@ -3544,9 +3579,9 @@
       <c r="D33" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
+      <c r="E33" s="64"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="64"/>
       <c r="H33" s="5" t="s">
         <v>89</v>
       </c>
@@ -3755,16 +3790,16 @@
       <c r="A41" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="B41" s="50" t="s">
+      <c r="B41" s="63" t="s">
         <v>155</v>
       </c>
-      <c r="C41" s="41"/>
-      <c r="D41" s="41"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="41"/>
-      <c r="G41" s="41"/>
-      <c r="H41" s="41"/>
-      <c r="I41" s="41"/>
+      <c r="C41" s="64"/>
+      <c r="D41" s="64"/>
+      <c r="E41" s="64"/>
+      <c r="F41" s="64"/>
+      <c r="G41" s="64"/>
+      <c r="H41" s="64"/>
+      <c r="I41" s="64"/>
     </row>
     <row r="42" spans="1:9" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
@@ -3835,13 +3870,13 @@
       <c r="D44" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E44" s="40" t="s">
+      <c r="E44" s="66" t="s">
         <v>173</v>
       </c>
       <c r="F44" s="31">
         <v>46353</v>
       </c>
-      <c r="G44" s="42" t="s">
+      <c r="G44" s="68" t="s">
         <v>69</v>
       </c>
       <c r="H44" s="5" t="s">
@@ -3864,11 +3899,11 @@
       <c r="D45" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="E45" s="41"/>
+      <c r="E45" s="64"/>
       <c r="F45" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G45" s="41"/>
+      <c r="G45" s="64"/>
       <c r="H45" s="5" t="s">
         <v>178</v>
       </c>
@@ -3887,11 +3922,11 @@
       <c r="D46" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="E46" s="41"/>
+      <c r="E46" s="64"/>
       <c r="F46" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G46" s="41"/>
+      <c r="G46" s="64"/>
       <c r="H46" s="5" t="s">
         <v>104</v>
       </c>
@@ -3910,11 +3945,11 @@
       <c r="D47" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="E47" s="41"/>
+      <c r="E47" s="64"/>
       <c r="F47" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G47" s="41"/>
+      <c r="G47" s="64"/>
       <c r="H47" s="5" t="s">
         <v>107</v>
       </c>
@@ -3933,11 +3968,11 @@
       <c r="D48" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="E48" s="41"/>
+      <c r="E48" s="64"/>
       <c r="F48" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G48" s="41"/>
+      <c r="G48" s="64"/>
       <c r="H48" s="5" t="s">
         <v>110</v>
       </c>
@@ -3956,11 +3991,11 @@
       <c r="D49" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="E49" s="41"/>
+      <c r="E49" s="64"/>
       <c r="F49" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G49" s="41"/>
+      <c r="G49" s="64"/>
       <c r="H49" s="5" t="s">
         <v>191</v>
       </c>
@@ -3979,11 +4014,11 @@
       <c r="D50" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E50" s="41"/>
+      <c r="E50" s="64"/>
       <c r="F50" s="31">
         <v>46353</v>
       </c>
-      <c r="G50" s="41"/>
+      <c r="G50" s="64"/>
       <c r="H50" s="5" t="s">
         <v>89</v>
       </c>
@@ -4002,13 +4037,13 @@
       <c r="D51" s="31">
         <v>46353</v>
       </c>
-      <c r="E51" s="40" t="s">
+      <c r="E51" s="66" t="s">
         <v>196</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="G51" s="42" t="s">
+      <c r="G51" s="68" t="s">
         <v>69</v>
       </c>
       <c r="H51" s="5" t="s">
@@ -4029,11 +4064,11 @@
       <c r="D52" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="E52" s="41"/>
+      <c r="E52" s="64"/>
       <c r="F52" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G52" s="41"/>
+      <c r="G52" s="64"/>
       <c r="H52" s="5" t="s">
         <v>201</v>
       </c>
@@ -4052,11 +4087,11 @@
       <c r="D53" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="E53" s="41"/>
+      <c r="E53" s="64"/>
       <c r="F53" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G53" s="41"/>
+      <c r="G53" s="64"/>
       <c r="H53" s="5" t="s">
         <v>89</v>
       </c>
@@ -4075,11 +4110,11 @@
       <c r="D54" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="E54" s="41"/>
+      <c r="E54" s="64"/>
       <c r="F54" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G54" s="41"/>
+      <c r="G54" s="64"/>
       <c r="H54" s="5" t="s">
         <v>89</v>
       </c>
@@ -4098,11 +4133,11 @@
       <c r="D55" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E55" s="41"/>
+      <c r="E55" s="64"/>
       <c r="F55" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G55" s="41"/>
+      <c r="G55" s="64"/>
       <c r="H55" s="5" t="s">
         <v>89</v>
       </c>
@@ -4121,11 +4156,11 @@
       <c r="D56" s="31">
         <v>46353</v>
       </c>
-      <c r="E56" s="41"/>
+      <c r="E56" s="64"/>
       <c r="F56" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="G56" s="41"/>
+      <c r="G56" s="64"/>
       <c r="H56" s="5" t="s">
         <v>89</v>
       </c>
@@ -4144,13 +4179,13 @@
       <c r="D57" s="31">
         <v>46353</v>
       </c>
-      <c r="E57" s="40" t="s">
+      <c r="E57" s="66" t="s">
         <v>212</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="G57" s="42" t="s">
+      <c r="G57" s="68" t="s">
         <v>69</v>
       </c>
       <c r="H57" s="5" t="s">
@@ -4173,11 +4208,11 @@
       <c r="D58" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="E58" s="41"/>
+      <c r="E58" s="64"/>
       <c r="F58" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G58" s="41"/>
+      <c r="G58" s="64"/>
       <c r="H58" s="5" t="s">
         <v>89</v>
       </c>
@@ -4196,11 +4231,11 @@
       <c r="D59" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="E59" s="41"/>
+      <c r="E59" s="64"/>
       <c r="F59" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="G59" s="41"/>
+      <c r="G59" s="64"/>
       <c r="H59" s="5" t="s">
         <v>89</v>
       </c>
@@ -4221,11 +4256,11 @@
       <c r="D60" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E60" s="41"/>
+      <c r="E60" s="64"/>
       <c r="F60" s="31">
         <v>46353</v>
       </c>
-      <c r="G60" s="41"/>
+      <c r="G60" s="64"/>
       <c r="H60" s="5" t="s">
         <v>222</v>
       </c>
@@ -4430,16 +4465,16 @@
       <c r="A69" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="B69" s="47" t="s">
+      <c r="B69" s="67" t="s">
         <v>256</v>
       </c>
-      <c r="C69" s="41"/>
-      <c r="D69" s="41"/>
-      <c r="E69" s="41"/>
-      <c r="F69" s="41"/>
-      <c r="G69" s="41"/>
-      <c r="H69" s="41"/>
-      <c r="I69" s="41"/>
+      <c r="C69" s="64"/>
+      <c r="D69" s="64"/>
+      <c r="E69" s="64"/>
+      <c r="F69" s="64"/>
+      <c r="G69" s="64"/>
+      <c r="H69" s="64"/>
+      <c r="I69" s="64"/>
     </row>
     <row r="70" spans="1:9" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
@@ -4801,10 +4836,10 @@
       <c r="E84" s="10"/>
     </row>
     <row r="85" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="49" t="s">
+      <c r="B85" s="62" t="s">
         <v>326</v>
       </c>
-      <c r="C85" s="45"/>
+      <c r="C85" s="60"/>
       <c r="D85" s="1" t="s">
         <v>327</v>
       </c>
@@ -4861,10 +4896,10 @@
       <c r="E93" s="10"/>
     </row>
     <row r="94" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="49" t="s">
+      <c r="B94" s="62" t="s">
         <v>334</v>
       </c>
-      <c r="C94" s="45"/>
+      <c r="C94" s="60"/>
       <c r="D94" s="1" t="s">
         <v>327</v>
       </c>
@@ -4892,6 +4927,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="G57:G60"/>
+    <mergeCell ref="E51:E56"/>
+    <mergeCell ref="F27:F33"/>
+    <mergeCell ref="G44:G50"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="B85:C85"/>
     <mergeCell ref="B94:C94"/>
@@ -4908,11 +4948,6 @@
     <mergeCell ref="E27:E33"/>
     <mergeCell ref="E21:E26"/>
     <mergeCell ref="G21:G26"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="G57:G60"/>
-    <mergeCell ref="E51:E56"/>
-    <mergeCell ref="F27:F33"/>
-    <mergeCell ref="G44:G50"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -4929,39 +4964,40 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="5" max="5" width="56.7109375" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="8" width="69.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="69" t="s">
         <v>338</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="41"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-    </row>
-    <row r="3" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+    </row>
+    <row r="3" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="38" t="s">
         <v>339</v>
       </c>
@@ -4984,535 +5020,573 @@
         <v>345</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="65" t="s">
+    <row r="4" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="71" t="s">
         <v>346</v>
       </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-    </row>
-    <row r="5" spans="1:7" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="76" t="s">
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+    </row>
+    <row r="5" spans="1:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="47" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="78">
+      <c r="D5" s="48">
         <v>46269</v>
       </c>
-      <c r="E5" s="77" t="s">
+      <c r="E5" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="F5" s="78">
+      <c r="F5" s="48">
         <v>46272</v>
       </c>
-      <c r="G5" s="76" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="67" t="s">
+      <c r="G5" s="46" t="s">
+        <v>459</v>
+      </c>
+      <c r="H5" s="55"/>
+      <c r="I5" s="56"/>
+    </row>
+    <row r="6" spans="1:9" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="46" t="s">
         <v>347</v>
       </c>
-      <c r="B6" s="68" t="s">
+      <c r="B6" s="47" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="67" t="s">
+      <c r="C6" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="D6" s="69">
+      <c r="D6" s="48">
         <v>46269</v>
       </c>
-      <c r="E6" s="68" t="s">
+      <c r="E6" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67" t="s">
+      <c r="F6" s="50">
+        <v>46296</v>
+      </c>
+      <c r="G6" s="46" t="s">
+        <v>459</v>
+      </c>
+      <c r="H6" s="55"/>
+    </row>
+    <row r="7" spans="1:9" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="48">
+        <v>46280</v>
+      </c>
+      <c r="E7" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="F7" s="50">
+        <v>46285</v>
+      </c>
+      <c r="G7" s="46" t="s">
+        <v>461</v>
+      </c>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="43">
+        <v>46295</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="49">
+        <v>46281</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>462</v>
+      </c>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="43">
+        <v>46295</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="49">
+        <v>46296</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>460</v>
+      </c>
+      <c r="H9" s="54"/>
+    </row>
+    <row r="10" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="53">
+        <v>46295</v>
+      </c>
+      <c r="E10" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="B7" s="68" t="s">
-        <v>138</v>
-      </c>
-      <c r="C7" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="69">
-        <v>46280</v>
-      </c>
-      <c r="E7" s="68" t="s">
-        <v>140</v>
-      </c>
-      <c r="F7" s="79">
-        <v>46285</v>
-      </c>
-      <c r="G7" s="67" t="s">
+      <c r="H10" s="57"/>
+    </row>
+    <row r="11" spans="1:9" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="52" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="D11" s="53">
+        <v>46295</v>
+      </c>
+      <c r="E11" s="52" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="43">
+        <v>46295</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="F12" s="49">
+        <v>46286</v>
+      </c>
+      <c r="G12" s="41" t="s">
+        <v>464</v>
+      </c>
+      <c r="H12" s="55"/>
+    </row>
+    <row r="13" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="85" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" s="86" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="87" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="87" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="86" t="s">
+        <v>144</v>
+      </c>
+      <c r="F13" s="88">
+        <v>46297</v>
+      </c>
+      <c r="G13" s="87" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="71" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="67" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="68" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="69">
-        <v>46295</v>
-      </c>
-      <c r="E8" s="68" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="79">
-        <v>46281</v>
-      </c>
-      <c r="G8" s="67" t="s">
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="72"/>
+    </row>
+    <row r="15" spans="1:9" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="43">
+        <v>46309</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="55"/>
+    </row>
+    <row r="16" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="41" t="s">
+        <v>280</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="43">
+        <v>46310</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>283</v>
+      </c>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="55"/>
+    </row>
+    <row r="17" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="43">
+        <v>46323</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="56"/>
+    </row>
+    <row r="19" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="71" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="73" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="74" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="75">
-        <v>46295</v>
-      </c>
-      <c r="E9" s="74" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73" t="s">
+      <c r="B19" s="72"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="72"/>
+    </row>
+    <row r="20" spans="1:8" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="B20" s="44" t="s">
+        <v>157</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="D20" s="45">
+        <v>46342</v>
+      </c>
+      <c r="E20" s="44" t="s">
+        <v>160</v>
+      </c>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+    </row>
+    <row r="21" spans="1:8" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="B21" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="D21" s="45">
+        <v>46342</v>
+      </c>
+      <c r="E21" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+    </row>
+    <row r="22" spans="1:8" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="B22" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="45">
+        <v>46353</v>
+      </c>
+      <c r="E22" s="44" t="s">
+        <v>173</v>
+      </c>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+    </row>
+    <row r="23" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="B23" s="44" t="s">
+        <v>195</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="45">
+        <v>46353</v>
+      </c>
+      <c r="E23" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+    </row>
+    <row r="24" spans="1:8" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="40" t="s">
+        <v>210</v>
+      </c>
+      <c r="B24" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="C24" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="45">
+        <v>46353</v>
+      </c>
+      <c r="E24" s="44" t="s">
+        <v>212</v>
+      </c>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+    </row>
+    <row r="25" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="B25" s="44" t="s">
+        <v>234</v>
+      </c>
+      <c r="C25" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="45">
+        <v>46353</v>
+      </c>
+      <c r="E25" s="44" t="s">
+        <v>235</v>
+      </c>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+    </row>
+    <row r="26" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="B26" s="44" t="s">
+        <v>239</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="45">
+        <v>46353</v>
+      </c>
+      <c r="E26" s="44" t="s">
+        <v>235</v>
+      </c>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+    </row>
+    <row r="27" spans="1:8" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="B27" s="44" t="s">
+        <v>248</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="45">
+        <v>46353</v>
+      </c>
+      <c r="E27" s="44" t="s">
+        <v>249</v>
+      </c>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+    </row>
+    <row r="28" spans="1:8" ht="78.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="B28" s="44" t="s">
+        <v>242</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="45">
+        <v>46356</v>
+      </c>
+      <c r="E28" s="44" t="s">
+        <v>244</v>
+      </c>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+    </row>
+    <row r="29" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="B29" s="44" t="s">
+        <v>252</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="45">
+        <v>46356</v>
+      </c>
+      <c r="E29" s="44" t="s">
+        <v>253</v>
+      </c>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="70" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="73" t="s">
-        <v>90</v>
-      </c>
-      <c r="B10" s="74" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="75">
-        <v>46295</v>
-      </c>
-      <c r="E10" s="74" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="73"/>
-      <c r="G10" s="73" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="73" t="s">
-        <v>130</v>
-      </c>
-      <c r="B11" s="74" t="s">
-        <v>131</v>
-      </c>
-      <c r="C11" s="73" t="s">
-        <v>132</v>
-      </c>
-      <c r="D11" s="75">
-        <v>46295</v>
-      </c>
-      <c r="E11" s="74" t="s">
-        <v>133</v>
-      </c>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="67" t="s">
-        <v>148</v>
-      </c>
-      <c r="B12" s="68" t="s">
-        <v>149</v>
-      </c>
-      <c r="C12" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="69">
-        <v>46295</v>
-      </c>
-      <c r="E12" s="68" t="s">
-        <v>150</v>
-      </c>
-      <c r="F12" s="79">
-        <v>46286</v>
-      </c>
-      <c r="G12" s="67" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="65" t="s">
-        <v>352</v>
-      </c>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-    </row>
-    <row r="15" spans="1:7" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="70" t="s">
-        <v>113</v>
-      </c>
-      <c r="B15" s="71" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="70" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="72">
-        <v>46309</v>
-      </c>
-      <c r="E15" s="71" t="s">
-        <v>116</v>
-      </c>
-      <c r="F15" s="70"/>
-      <c r="G15" s="70"/>
-    </row>
-    <row r="16" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="70" t="s">
-        <v>280</v>
-      </c>
-      <c r="B16" s="71" t="s">
-        <v>281</v>
-      </c>
-      <c r="C16" s="70" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="72">
-        <v>46310</v>
-      </c>
-      <c r="E16" s="71" t="s">
-        <v>283</v>
-      </c>
-      <c r="F16" s="70"/>
-      <c r="G16" s="70"/>
-    </row>
-    <row r="17" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="70" t="s">
-        <v>269</v>
-      </c>
-      <c r="B17" s="71" t="s">
-        <v>270</v>
-      </c>
-      <c r="C17" s="70" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="72">
-        <v>46323</v>
-      </c>
-      <c r="E17" s="71" t="s">
-        <v>272</v>
-      </c>
-      <c r="F17" s="70"/>
-      <c r="G17" s="70"/>
-    </row>
-    <row r="19" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="65" t="s">
-        <v>353</v>
-      </c>
-      <c r="B19" s="66"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66"/>
-    </row>
-    <row r="20" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="70" t="s">
-        <v>156</v>
-      </c>
-      <c r="B20" s="71" t="s">
-        <v>157</v>
-      </c>
-      <c r="C20" s="70" t="s">
-        <v>158</v>
-      </c>
-      <c r="D20" s="72">
-        <v>46342</v>
-      </c>
-      <c r="E20" s="71" t="s">
-        <v>160</v>
-      </c>
-      <c r="F20" s="70"/>
-      <c r="G20" s="70"/>
-    </row>
-    <row r="21" spans="1:7" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="70" t="s">
-        <v>164</v>
-      </c>
-      <c r="B21" s="71" t="s">
-        <v>165</v>
-      </c>
-      <c r="C21" s="70" t="s">
-        <v>166</v>
-      </c>
-      <c r="D21" s="72">
-        <v>46342</v>
-      </c>
-      <c r="E21" s="71" t="s">
-        <v>167</v>
-      </c>
-      <c r="F21" s="70"/>
-      <c r="G21" s="70"/>
-    </row>
-    <row r="22" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="70" t="s">
-        <v>170</v>
-      </c>
-      <c r="B22" s="71" t="s">
-        <v>171</v>
-      </c>
-      <c r="C22" s="70" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="72">
-        <v>46353</v>
-      </c>
-      <c r="E22" s="71" t="s">
-        <v>173</v>
-      </c>
-      <c r="F22" s="70"/>
-      <c r="G22" s="70"/>
-    </row>
-    <row r="23" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="70" t="s">
-        <v>194</v>
-      </c>
-      <c r="B23" s="71" t="s">
-        <v>195</v>
-      </c>
-      <c r="C23" s="70" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="72">
-        <v>46353</v>
-      </c>
-      <c r="E23" s="71" t="s">
-        <v>196</v>
-      </c>
-      <c r="F23" s="70"/>
-      <c r="G23" s="70"/>
-    </row>
-    <row r="24" spans="1:7" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="70" t="s">
-        <v>210</v>
-      </c>
-      <c r="B24" s="71" t="s">
-        <v>211</v>
-      </c>
-      <c r="C24" s="70" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="72">
-        <v>46353</v>
-      </c>
-      <c r="E24" s="71" t="s">
-        <v>212</v>
-      </c>
-      <c r="F24" s="70"/>
-      <c r="G24" s="70"/>
-    </row>
-    <row r="25" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="70" t="s">
-        <v>233</v>
-      </c>
-      <c r="B25" s="71" t="s">
-        <v>234</v>
-      </c>
-      <c r="C25" s="70" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="72">
-        <v>46353</v>
-      </c>
-      <c r="E25" s="71" t="s">
-        <v>235</v>
-      </c>
-      <c r="F25" s="70"/>
-      <c r="G25" s="70"/>
-    </row>
-    <row r="26" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="70" t="s">
-        <v>238</v>
-      </c>
-      <c r="B26" s="71" t="s">
-        <v>239</v>
-      </c>
-      <c r="C26" s="70" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="72">
-        <v>46353</v>
-      </c>
-      <c r="E26" s="71" t="s">
-        <v>235</v>
-      </c>
-      <c r="F26" s="70"/>
-      <c r="G26" s="70"/>
-    </row>
-    <row r="27" spans="1:7" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="70" t="s">
-        <v>247</v>
-      </c>
-      <c r="B27" s="71" t="s">
-        <v>248</v>
-      </c>
-      <c r="C27" s="70" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27" s="72">
-        <v>46353</v>
-      </c>
-      <c r="E27" s="71" t="s">
-        <v>249</v>
-      </c>
-      <c r="F27" s="70"/>
-      <c r="G27" s="70"/>
-    </row>
-    <row r="28" spans="1:7" ht="78.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="70" t="s">
-        <v>241</v>
-      </c>
-      <c r="B28" s="71" t="s">
-        <v>242</v>
-      </c>
-      <c r="C28" s="70" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="72">
-        <v>46356</v>
-      </c>
-      <c r="E28" s="71" t="s">
-        <v>244</v>
-      </c>
-      <c r="F28" s="70"/>
-      <c r="G28" s="70"/>
-    </row>
-    <row r="29" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="70" t="s">
-        <v>251</v>
-      </c>
-      <c r="B29" s="71" t="s">
-        <v>252</v>
-      </c>
-      <c r="C29" s="70" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" s="72">
-        <v>46356</v>
-      </c>
-      <c r="E29" s="71" t="s">
-        <v>253</v>
-      </c>
-      <c r="F29" s="70"/>
-      <c r="G29" s="70"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="64"/>
+      <c r="C31" s="64"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="64"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="64"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="39" t="s">
         <v>257</v>
       </c>
-      <c r="B32" s="53" t="s">
-        <v>355</v>
-      </c>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
+      <c r="B32" s="75" t="s">
+        <v>351</v>
+      </c>
+      <c r="C32" s="64"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="64"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="64"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="39" t="s">
         <v>290</v>
       </c>
-      <c r="B33" s="53" t="s">
-        <v>356</v>
-      </c>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
+      <c r="B33" s="75" t="s">
+        <v>352</v>
+      </c>
+      <c r="C33" s="64"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="64"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="64"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="39" t="s">
         <v>294</v>
       </c>
-      <c r="B34" s="53" t="s">
-        <v>357</v>
-      </c>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
+      <c r="B34" s="75" t="s">
+        <v>353</v>
+      </c>
+      <c r="C34" s="64"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="64"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="64"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="39" t="s">
         <v>300</v>
       </c>
-      <c r="B35" s="53" t="s">
-        <v>358</v>
-      </c>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
+      <c r="B35" s="75" t="s">
+        <v>354</v>
+      </c>
+      <c r="C35" s="64"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="64"/>
+      <c r="F35" s="64"/>
+      <c r="G35" s="64"/>
     </row>
     <row r="38" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="51" t="s">
-        <v>359</v>
-      </c>
-      <c r="B38" s="52"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
+      <c r="A38" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="B38" s="74"/>
+      <c r="C38" s="74"/>
+      <c r="D38" s="74"/>
+      <c r="E38" s="74"/>
+      <c r="F38" s="74"/>
+      <c r="G38" s="74"/>
     </row>
     <row r="39" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="38" t="s">
@@ -5538,234 +5612,237 @@
       </c>
     </row>
     <row r="40" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="76" t="s">
+      <c r="A40" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="B40" s="77" t="s">
+      <c r="B40" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="76" t="s">
+      <c r="C40" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="D40" s="78">
+      <c r="D40" s="48">
         <v>46268</v>
       </c>
-      <c r="E40" s="77" t="s">
+      <c r="E40" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="F40" s="78">
+      <c r="F40" s="48">
         <v>46261</v>
       </c>
-      <c r="G40" s="76" t="s">
+      <c r="G40" s="46" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="48">
+        <v>46258</v>
+      </c>
+      <c r="E41" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="F41" s="48">
+        <v>46266</v>
+      </c>
+      <c r="G41" s="46" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="48">
+        <v>46261</v>
+      </c>
+      <c r="E42" s="47" t="s">
+        <v>58</v>
+      </c>
+      <c r="F42" s="48">
+        <v>46267</v>
+      </c>
+      <c r="G42" s="46" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="46" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="48">
+        <v>46261</v>
+      </c>
+      <c r="E43" s="47" t="s">
+        <v>359</v>
+      </c>
+      <c r="F43" s="48">
+        <v>46267</v>
+      </c>
+      <c r="G43" s="46" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="B44" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="48">
+        <v>46261</v>
+      </c>
+      <c r="E44" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" s="48">
+        <v>46269</v>
+      </c>
+      <c r="G44" s="46" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="B45" s="47" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="76" t="s">
-        <v>52</v>
-      </c>
-      <c r="B41" s="77" t="s">
-        <v>53</v>
-      </c>
-      <c r="C41" s="76" t="s">
-        <v>18</v>
-      </c>
-      <c r="D41" s="78">
-        <v>46258</v>
-      </c>
-      <c r="E41" s="77" t="s">
+      <c r="C45" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="48">
+        <v>46268</v>
+      </c>
+      <c r="E45" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="F45" s="48">
+        <v>46269</v>
+      </c>
+      <c r="G45" s="46" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="46"/>
+      <c r="B46" s="47" t="s">
+        <v>361</v>
+      </c>
+      <c r="C46" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="48">
+        <v>46237</v>
+      </c>
+      <c r="E46" s="47" t="s">
+        <v>362</v>
+      </c>
+      <c r="F46" s="48">
+        <v>46272</v>
+      </c>
+      <c r="G46" s="46" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" s="48">
+        <v>46295</v>
+      </c>
+      <c r="E47" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="F47" s="48">
+        <v>46279</v>
+      </c>
+      <c r="G47" s="46" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="C48" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" s="48">
+        <v>46267</v>
+      </c>
+      <c r="E48" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="F41" s="78">
-        <v>46266</v>
-      </c>
-      <c r="G41" s="76" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="76" t="s">
-        <v>56</v>
-      </c>
-      <c r="B42" s="77" t="s">
-        <v>57</v>
-      </c>
-      <c r="C42" s="76" t="s">
-        <v>18</v>
-      </c>
-      <c r="D42" s="78">
-        <v>46261</v>
-      </c>
-      <c r="E42" s="77" t="s">
-        <v>58</v>
-      </c>
-      <c r="F42" s="78">
-        <v>46267</v>
-      </c>
-      <c r="G42" s="76" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="B43" s="77" t="s">
-        <v>72</v>
-      </c>
-      <c r="C43" s="76" t="s">
-        <v>18</v>
-      </c>
-      <c r="D43" s="78">
-        <v>46261</v>
-      </c>
-      <c r="E43" s="77" t="s">
-        <v>363</v>
-      </c>
-      <c r="F43" s="78">
-        <v>46267</v>
-      </c>
-      <c r="G43" s="76" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="76" t="s">
-        <v>16</v>
-      </c>
-      <c r="B44" s="77" t="s">
-        <v>17</v>
-      </c>
-      <c r="C44" s="76" t="s">
-        <v>18</v>
-      </c>
-      <c r="D44" s="78">
-        <v>46261</v>
-      </c>
-      <c r="E44" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="F44" s="78">
-        <v>46269</v>
-      </c>
-      <c r="G44" s="76" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="76" t="s">
-        <v>31</v>
-      </c>
-      <c r="B45" s="77" t="s">
+      <c r="F48" s="48">
+        <v>46293</v>
+      </c>
+      <c r="G48" s="46" t="s">
         <v>364</v>
       </c>
-      <c r="C45" s="76" t="s">
-        <v>18</v>
-      </c>
-      <c r="D45" s="78">
-        <v>46268</v>
-      </c>
-      <c r="E45" s="77" t="s">
-        <v>33</v>
-      </c>
-      <c r="F45" s="78">
-        <v>46269</v>
-      </c>
-      <c r="G45" s="76" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="76"/>
-      <c r="B46" s="77" t="s">
+    </row>
+    <row r="49" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="B49" s="47" t="s">
+        <v>143</v>
+      </c>
+      <c r="C49" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="48">
+        <v>46295</v>
+      </c>
+      <c r="E49" s="47" t="s">
+        <v>144</v>
+      </c>
+      <c r="F49" s="46"/>
+      <c r="G49" s="46" t="s">
         <v>365</v>
-      </c>
-      <c r="C46" s="76" t="s">
-        <v>18</v>
-      </c>
-      <c r="D46" s="78">
-        <v>46237</v>
-      </c>
-      <c r="E46" s="77" t="s">
-        <v>366</v>
-      </c>
-      <c r="F46" s="78">
-        <v>46272</v>
-      </c>
-      <c r="G46" s="76" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="76" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="77" t="s">
-        <v>41</v>
-      </c>
-      <c r="C47" s="76" t="s">
-        <v>18</v>
-      </c>
-      <c r="D47" s="78">
-        <v>46295</v>
-      </c>
-      <c r="E47" s="77" t="s">
-        <v>42</v>
-      </c>
-      <c r="F47" s="78">
-        <v>46279</v>
-      </c>
-      <c r="G47" s="76" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="76" t="s">
-        <v>46</v>
-      </c>
-      <c r="B48" s="77" t="s">
-        <v>47</v>
-      </c>
-      <c r="C48" s="76" t="s">
-        <v>18</v>
-      </c>
-      <c r="D48" s="78">
-        <v>46267</v>
-      </c>
-      <c r="E48" s="77" t="s">
-        <v>49</v>
-      </c>
-      <c r="F48" s="78">
-        <v>46293</v>
-      </c>
-      <c r="G48" s="76" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="76" t="s">
-        <v>142</v>
-      </c>
-      <c r="B49" s="77" t="s">
-        <v>143</v>
-      </c>
-      <c r="C49" s="76" t="s">
-        <v>18</v>
-      </c>
-      <c r="D49" s="78">
-        <v>46295</v>
-      </c>
-      <c r="E49" s="77" t="s">
-        <v>144</v>
-      </c>
-      <c r="F49" s="76"/>
-      <c r="G49" s="76" t="s">
-        <v>369</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:G29" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="11">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A38:G38"/>
     <mergeCell ref="B35:G35"/>
     <mergeCell ref="B32:G32"/>
@@ -5774,9 +5851,6 @@
     <mergeCell ref="B33:G33"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="B34:G34"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
@@ -5805,35 +5879,35 @@
     </row>
     <row r="2" spans="2:9" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="C2" s="76" t="s">
+        <v>367</v>
+      </c>
+      <c r="D2" s="76" t="s">
+        <v>368</v>
+      </c>
+      <c r="E2" s="76" t="s">
+        <v>369</v>
+      </c>
+      <c r="F2" s="64"/>
+      <c r="G2" s="76" t="s">
         <v>370</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>371</v>
-      </c>
-      <c r="D2" s="58" t="s">
-        <v>372</v>
-      </c>
-      <c r="E2" s="58" t="s">
-        <v>373</v>
-      </c>
-      <c r="F2" s="41"/>
-      <c r="G2" s="58" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="17" t="s">
-        <v>375</v>
-      </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
+        <v>371</v>
+      </c>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
       <c r="E3" s="17" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>377</v>
-      </c>
-      <c r="G3" s="41"/>
+        <v>373</v>
+      </c>
+      <c r="G3" s="64"/>
     </row>
     <row r="4" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="17">
@@ -5856,376 +5930,376 @@
       </c>
     </row>
     <row r="5" spans="2:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="56">
+      <c r="B5" s="77">
         <v>1</v>
       </c>
-      <c r="C5" s="59" t="s">
+      <c r="C5" s="79" t="s">
+        <v>374</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>375</v>
+      </c>
+      <c r="E5" s="77" t="s">
+        <v>376</v>
+      </c>
+      <c r="F5" s="80">
+        <v>46386</v>
+      </c>
+      <c r="G5" s="78">
+        <v>92947038.540000007</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+    </row>
+    <row r="7" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="18" t="s">
         <v>378</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+    </row>
+    <row r="8" spans="2:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="18" t="s">
         <v>379</v>
       </c>
-      <c r="E5" s="56" t="s">
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+    </row>
+    <row r="9" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="64"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="18" t="s">
         <v>380</v>
       </c>
-      <c r="F5" s="57">
-        <v>46386</v>
-      </c>
-      <c r="G5" s="60">
-        <v>92947038.540000007</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="18" t="s">
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+    </row>
+    <row r="10" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="18" t="s">
         <v>381</v>
       </c>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-    </row>
-    <row r="7" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="18" t="s">
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+    </row>
+    <row r="11" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="18" t="s">
         <v>382</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-    </row>
-    <row r="8" spans="2:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="18" t="s">
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+    </row>
+    <row r="12" spans="2:9" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="18" t="s">
         <v>383</v>
       </c>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-    </row>
-    <row r="9" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="18" t="s">
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+    </row>
+    <row r="13" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="77">
+        <v>2</v>
+      </c>
+      <c r="C13" s="79" t="s">
         <v>384</v>
       </c>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-    </row>
-    <row r="10" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="18" t="s">
+      <c r="D13" s="18" t="s">
         <v>385</v>
       </c>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-    </row>
-    <row r="11" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="18" t="s">
+      <c r="E13" s="80">
+        <v>46388</v>
+      </c>
+      <c r="F13" s="80">
+        <v>46568</v>
+      </c>
+      <c r="G13" s="78">
+        <v>79995696.700000003</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="18" t="s">
         <v>386</v>
       </c>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-    </row>
-    <row r="12" spans="2:9" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="18" t="s">
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+    </row>
+    <row r="15" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="64"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="18" t="s">
         <v>387</v>
       </c>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-    </row>
-    <row r="13" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="56">
-        <v>2</v>
-      </c>
-      <c r="C13" s="59" t="s">
+      <c r="E15" s="64"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
+    </row>
+    <row r="16" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="64"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="18" t="s">
         <v>388</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="E16" s="64"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="64"/>
+    </row>
+    <row r="17" spans="2:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="64"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="18" t="s">
         <v>389</v>
       </c>
-      <c r="E13" s="57">
-        <v>46388</v>
-      </c>
-      <c r="F13" s="57">
-        <v>46568</v>
-      </c>
-      <c r="G13" s="60">
-        <v>79995696.700000003</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="18" t="s">
+      <c r="E17" s="64"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="64"/>
+    </row>
+    <row r="18" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="64"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="18" t="s">
         <v>390</v>
       </c>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-    </row>
-    <row r="15" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="18" t="s">
+      <c r="E18" s="64"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="64"/>
+    </row>
+    <row r="19" spans="2:7" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="64"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="18" t="s">
         <v>391</v>
       </c>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-    </row>
-    <row r="16" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="18" t="s">
+      <c r="E19" s="64"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="64"/>
+    </row>
+    <row r="20" spans="2:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="77">
+        <v>3</v>
+      </c>
+      <c r="C20" s="79" t="s">
         <v>392</v>
       </c>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-    </row>
-    <row r="17" spans="2:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="41"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="18" t="s">
+      <c r="D20" s="18" t="s">
         <v>393</v>
       </c>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-    </row>
-    <row r="18" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="18" t="s">
+      <c r="E20" s="80">
+        <v>46569</v>
+      </c>
+      <c r="F20" s="80">
+        <v>46751</v>
+      </c>
+      <c r="G20" s="78">
+        <v>88797441.670000002</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="64"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="18" t="s">
         <v>394</v>
       </c>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-    </row>
-    <row r="19" spans="2:7" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="41"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="18" t="s">
+      <c r="E21" s="64"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+    </row>
+    <row r="22" spans="2:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="64"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="18" t="s">
         <v>395</v>
       </c>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-    </row>
-    <row r="20" spans="2:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="56">
-        <v>3</v>
-      </c>
-      <c r="C20" s="59" t="s">
+      <c r="E22" s="64"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="64"/>
+    </row>
+    <row r="23" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="64"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="18" t="s">
         <v>396</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="E23" s="64"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="64"/>
+    </row>
+    <row r="24" spans="2:7" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="64"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="18" t="s">
         <v>397</v>
       </c>
-      <c r="E20" s="57">
-        <v>46569</v>
-      </c>
-      <c r="F20" s="57">
-        <v>46751</v>
-      </c>
-      <c r="G20" s="60">
-        <v>88797441.670000002</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="18" t="s">
+      <c r="E24" s="64"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="64"/>
+    </row>
+    <row r="25" spans="2:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="77">
+        <v>4</v>
+      </c>
+      <c r="C25" s="79" t="s">
         <v>398</v>
       </c>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-    </row>
-    <row r="22" spans="2:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="18" t="s">
+      <c r="D25" s="18" t="s">
         <v>399</v>
       </c>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-    </row>
-    <row r="23" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="18" t="s">
+      <c r="E25" s="80">
+        <v>46753</v>
+      </c>
+      <c r="F25" s="80">
+        <v>46934</v>
+      </c>
+      <c r="G25" s="78">
+        <v>92796812.010000005</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="64"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="18" t="s">
         <v>400</v>
       </c>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-    </row>
-    <row r="24" spans="2:7" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="41"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="18" t="s">
+      <c r="E26" s="64"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="64"/>
+    </row>
+    <row r="27" spans="2:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="64"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="18" t="s">
         <v>401</v>
       </c>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-    </row>
-    <row r="25" spans="2:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="56">
-        <v>4</v>
-      </c>
-      <c r="C25" s="59" t="s">
+      <c r="E27" s="64"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="64"/>
+    </row>
+    <row r="28" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="64"/>
+      <c r="C28" s="64"/>
+      <c r="D28" s="18" t="s">
         <v>402</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="E28" s="64"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="64"/>
+    </row>
+    <row r="29" spans="2:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="64"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="18" t="s">
         <v>403</v>
       </c>
-      <c r="E25" s="57">
-        <v>46753</v>
-      </c>
-      <c r="F25" s="57">
-        <v>46934</v>
-      </c>
-      <c r="G25" s="60">
-        <v>92796812.010000005</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="41"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="18" t="s">
+      <c r="E29" s="64"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
+    </row>
+    <row r="30" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="77">
+        <v>5</v>
+      </c>
+      <c r="C30" s="79" t="s">
         <v>404</v>
       </c>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-    </row>
-    <row r="27" spans="2:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="41"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="18" t="s">
+      <c r="D30" s="18" t="s">
         <v>405</v>
       </c>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-    </row>
-    <row r="28" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="18" t="s">
+      <c r="E30" s="80">
+        <v>46935</v>
+      </c>
+      <c r="F30" s="80">
+        <v>47117</v>
+      </c>
+      <c r="G30" s="78">
+        <v>54867026.329999998</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="64"/>
+      <c r="C31" s="64"/>
+      <c r="D31" s="18" t="s">
         <v>406</v>
       </c>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-    </row>
-    <row r="29" spans="2:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="18" t="s">
+      <c r="E31" s="64"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="64"/>
+    </row>
+    <row r="32" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="64"/>
+      <c r="C32" s="64"/>
+      <c r="D32" s="18" t="s">
         <v>407</v>
       </c>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-    </row>
-    <row r="30" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="56">
-        <v>5</v>
-      </c>
-      <c r="C30" s="59" t="s">
+      <c r="E32" s="64"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="64"/>
+    </row>
+    <row r="33" spans="2:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="64"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="18" t="s">
         <v>408</v>
       </c>
-      <c r="D30" s="18" t="s">
-        <v>409</v>
-      </c>
-      <c r="E30" s="57">
-        <v>46935</v>
-      </c>
-      <c r="F30" s="57">
-        <v>47117</v>
-      </c>
-      <c r="G30" s="60">
-        <v>54867026.329999998</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="18" t="s">
-        <v>410</v>
-      </c>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-    </row>
-    <row r="32" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="41"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="18" t="s">
-        <v>411</v>
-      </c>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
-    </row>
-    <row r="33" spans="2:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="41"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="18" t="s">
-        <v>412</v>
-      </c>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
+      <c r="E33" s="64"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="G25:G29"/>
+    <mergeCell ref="B13:B19"/>
+    <mergeCell ref="E20:E24"/>
+    <mergeCell ref="F13:F19"/>
+    <mergeCell ref="F30:F33"/>
     <mergeCell ref="G30:G33"/>
-    <mergeCell ref="E2:F2"/>
     <mergeCell ref="B25:B29"/>
     <mergeCell ref="F25:F29"/>
     <mergeCell ref="B30:B33"/>
-    <mergeCell ref="E20:E24"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="E25:E29"/>
+    <mergeCell ref="C25:C29"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="B5:B12"/>
+    <mergeCell ref="G20:G24"/>
+    <mergeCell ref="C13:C19"/>
     <mergeCell ref="G5:G12"/>
     <mergeCell ref="F20:F24"/>
     <mergeCell ref="E13:E19"/>
     <mergeCell ref="C20:C24"/>
-    <mergeCell ref="C25:C29"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="B5:B12"/>
-    <mergeCell ref="G20:G24"/>
-    <mergeCell ref="C13:C19"/>
-    <mergeCell ref="E25:E29"/>
-    <mergeCell ref="B20:B24"/>
-    <mergeCell ref="G25:G29"/>
-    <mergeCell ref="B13:B19"/>
-    <mergeCell ref="F30:F33"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="F13:F19"/>
     <mergeCell ref="C5:C12"/>
     <mergeCell ref="E5:E12"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="F5:F12"/>
-    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="B20:B24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -6245,24 +6319,24 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="20" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>412</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="F2" s="19" t="s">
         <v>414</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>415</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>417</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6270,10 +6344,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="E3" s="21">
         <v>4000000</v>
@@ -6285,10 +6359,10 @@
         <v>62</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="E4" s="21">
         <v>1000000</v>
@@ -6296,13 +6370,13 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="59" t="s">
-        <v>423</v>
-      </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
+      <c r="B5" s="79" t="s">
+        <v>419</v>
+      </c>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
       <c r="E5" s="19" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="F5" s="18"/>
     </row>
@@ -6319,54 +6393,55 @@
   <dimension ref="B1:H37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="41.42578125" customWidth="1"/>
+    <col min="3" max="3" width="45.140625" customWidth="1"/>
+    <col min="6" max="7" width="15.28515625" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="37" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="H1" s="63"/>
+      <c r="H1" s="83"/>
     </row>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="62"/>
-      <c r="C2" s="41"/>
-      <c r="H2" s="64"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="64"/>
+      <c r="H2" s="84"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="22" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
       <c r="G3" s="22"/>
-      <c r="H3" s="41"/>
+      <c r="H3" s="64"/>
     </row>
     <row r="4" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="23" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C4" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>423</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>424</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>425</v>
+      </c>
+      <c r="G4" s="23" t="s">
         <v>426</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>427</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>428</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>429</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>430</v>
       </c>
       <c r="H4" s="36"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="22"/>
       <c r="C5" s="24" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="23"/>
@@ -6379,10 +6454,10 @@
         <v>14</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E6" s="23">
         <v>1</v>
@@ -6395,17 +6470,17 @@
         <f>F6*E6</f>
         <v>4590</v>
       </c>
-      <c r="H6" s="61"/>
+      <c r="H6" s="81"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="23" t="s">
         <v>62</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E7" s="23">
         <v>1</v>
@@ -6418,17 +6493,17 @@
         <f>F7*E7</f>
         <v>4136</v>
       </c>
-      <c r="H7" s="41"/>
-    </row>
-    <row r="8" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H7" s="64"/>
+    </row>
+    <row r="8" spans="2:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="23" t="s">
         <v>255</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E8" s="23">
         <v>1</v>
@@ -6444,13 +6519,13 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="23" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E9" s="23">
         <v>1</v>
@@ -6467,7 +6542,7 @@
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="24"/>
       <c r="C10" s="24" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="D10" s="26"/>
       <c r="E10" s="26"/>
@@ -6481,7 +6556,7 @@
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="22"/>
       <c r="C11" s="24" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D11" s="23"/>
       <c r="E11" s="23"/>
@@ -6494,10 +6569,10 @@
         <v>14</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E12" s="23">
         <v>2</v>
@@ -6516,10 +6591,10 @@
         <v>62</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E13" s="23">
         <v>1</v>
@@ -6538,10 +6613,10 @@
         <v>255</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E14" s="23">
         <v>2</v>
@@ -6558,7 +6633,7 @@
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="24"/>
       <c r="C15" s="24" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="D15" s="26"/>
       <c r="E15" s="23"/>
@@ -6572,7 +6647,7 @@
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="22"/>
       <c r="C16" s="24" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24"/>
@@ -6591,7 +6666,7 @@
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="22" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C19" s="22"/>
       <c r="D19" s="26"/>
@@ -6602,29 +6677,29 @@
     </row>
     <row r="20" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="23" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="H20" s="36"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="23"/>
       <c r="C21" s="24" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="23"/>
@@ -6632,15 +6707,15 @@
       <c r="G21" s="23"/>
       <c r="H21" s="36"/>
     </row>
-    <row r="22" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="23" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E22" s="23">
         <v>1</v>
@@ -6654,15 +6729,15 @@
       </c>
       <c r="H22" s="36"/>
     </row>
-    <row r="23" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="23" t="s">
         <v>62</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E23" s="23">
         <v>1</v>
@@ -6676,15 +6751,15 @@
       </c>
       <c r="H23" s="36"/>
     </row>
-    <row r="24" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="23" t="s">
         <v>255</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E24" s="23">
         <v>1</v>
@@ -6698,15 +6773,15 @@
       </c>
       <c r="H24" s="36"/>
     </row>
-    <row r="25" spans="2:8" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="23" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E25" s="23">
         <v>1</v>
@@ -6720,15 +6795,15 @@
       </c>
       <c r="H25" s="36"/>
     </row>
-    <row r="26" spans="2:8" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="23" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E26" s="23">
         <v>1</v>
@@ -6745,7 +6820,7 @@
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="24"/>
       <c r="C27" s="26" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="D27" s="23"/>
       <c r="E27" s="23"/>
@@ -6759,7 +6834,7 @@
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="24"/>
       <c r="C28" s="24" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D28" s="23"/>
       <c r="E28" s="23"/>
@@ -6767,15 +6842,15 @@
       <c r="G28" s="35"/>
       <c r="H28" s="36"/>
     </row>
-    <row r="29" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="23" t="s">
         <v>14</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E29" s="23">
         <v>1</v>
@@ -6789,15 +6864,15 @@
       </c>
       <c r="H29" s="36"/>
     </row>
-    <row r="30" spans="2:8" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="23" t="s">
         <v>62</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E30" s="23">
         <v>1</v>
@@ -6811,15 +6886,15 @@
       </c>
       <c r="H30" s="36"/>
     </row>
-    <row r="31" spans="2:8" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="23" t="s">
         <v>255</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E31" s="23">
         <v>1</v>
@@ -6833,15 +6908,15 @@
       </c>
       <c r="H31" s="36"/>
     </row>
-    <row r="32" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="23" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E32" s="23">
         <v>1</v>
@@ -6855,15 +6930,15 @@
       </c>
       <c r="H32" s="36"/>
     </row>
-    <row r="33" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="23" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E33" s="23">
         <v>1</v>
@@ -6877,15 +6952,15 @@
       </c>
       <c r="H33" s="36"/>
     </row>
-    <row r="34" spans="2:8" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="23" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E34" s="23">
         <v>1</v>
@@ -6901,13 +6976,13 @@
     </row>
     <row r="35" spans="2:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="23" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E35" s="23">
         <v>1</v>
@@ -6924,7 +6999,7 @@
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="24"/>
       <c r="C36" s="26" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="D36" s="23"/>
       <c r="E36" s="23"/>
@@ -6938,7 +7013,7 @@
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="22"/>
       <c r="C37" s="30" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="D37" s="24"/>
       <c r="E37" s="24"/>
